--- a/Oo.xlsx
+++ b/Oo.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4965" yWindow="8100" windowWidth="23010" windowHeight="17820" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -500,4 +500,3994 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ARR</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lilah</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Zim</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>34947428</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>09/04/1978</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zim</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>35134168</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10/11/2002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Itay</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bachar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>40811474</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>06/21/2016</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Zim</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>42509977</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10/21/2016</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hen Michael</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Oron</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dabbah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>42666121</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>07/25/1966</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gefen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Oron</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>35613979</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>03/15/2015</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tevel</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Oron</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>35619612</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11/13/2012</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rusainee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nantha Aphipong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08/18/2000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Urai</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Naiyana</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>11/21/1961</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kalinin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>758372349</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>04/04/2003</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tatiana</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kalinina</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>773245745</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12/09/1977</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sergei</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kalinin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>773126318</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08/02/1966</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thanyaluk</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Buathong</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08/22/1998</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pimporn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hemrat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>03/17/1960</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pattraporn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tongrit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>11/24/1976</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dubrovin</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>41336777</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>09/27/1983</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubrovin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>40090126</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>04/24/2012</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Roni</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubrovin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>40109442</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>04/05/2011</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Carmen Maree</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Greenhill</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PB4215303</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>05/15/1977</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Matthew Byron</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Greenhill</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PB3047057</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>09/03/1975</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Alannah Maree</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Greenhill</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PB4227658</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>07/29/2010</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bridget Carmen</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Greenhill</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PB4705835</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>07/01/2014</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Daniel Warwick</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Greenhill</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PB4227679</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>09/10/2008</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kelly Ann</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Parker</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RA6294943</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>05/05/1990</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Zoey Ann</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Parker</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RA1102741</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>12/14/2020</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Zane Lawrence</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Parker</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RA5552607</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>05/31/2019</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mitchell Daine</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Parker</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RA6181807</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>11/14/1988</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Grant James</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wolfel</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PA6284807</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>11/02/1983</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Edward James</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wolfel</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PB5188808</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>04/20/2017</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sarah Elizabeth</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wolfel</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RA6949831</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>09/05/1983</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jack Grant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wolfel</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RA6059493</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>08/24/2023</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sophie Grace</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Wolfel</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PB6339145</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>05/08/2019</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sarah Ann</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hartley</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PB6176114</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>02/08/1990</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>07/16/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Adam Lee</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Clarke</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PB4687758</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>01/24/1987</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>07/16/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Riley Hartley</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Clarke</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RA5905033</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>07/15/2023</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>07/16/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Paige Hartley</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Clarke</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PB6252899</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10/15/2019</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>07/16/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gerard</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Francisduignan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10/16/1984</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sinit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Duignan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>05/03/1985</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Nitsan</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Vaknin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>42207675</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>03/18/1984</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Rani</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Vaknin</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>42980162</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lavie</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vaknin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>42200373</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>11/11/2019</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tom Raphael</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Vaknin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>42202548</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>11/03/2015</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Yael Viki</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vaknin Gaizler</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>33153656</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10/27/1987</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>David James</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>120297461</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>11/11/1978</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ruby Rose</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>157875017</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>04/16/2011</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Beverley Louise</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>557796941</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>01/22/1976</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Florence Rose</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>128764091</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10/15/2017</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>David James</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>120297461</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>11/11/1978</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Margaret Rose</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>159875255</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>11/18/2015</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Constance Rose</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>157409532</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>11/18/2015</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Andrew George</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deane</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RA5109542</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>12/22/1971</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Zoe Louisa</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deane</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PB5197823</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>12/09/2014</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aletia Maree</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deane</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RA9752915</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>04/29/1978</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Lily Elise</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deane</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PB4748359</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>11/10/2010</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Lirit</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bachar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>37837824</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>12/18/1981</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Lia</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bachar</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>40812440</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>08/21/2009</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Yakov</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Bachar</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>43051860</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>02/21/1981</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Roni</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bachar</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40818730</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>06/01/2013</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Liran Yehuda</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Bachar</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40819657</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>04/21/2011</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Maayan</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Oron</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>24688189</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10/23/1988</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hen Michael</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Oron</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40082484</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>12/10/1984</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Shoham</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Oron</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40089310</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>02/02/2018</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Anantha Aphipon</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>08/30/1998</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aimulloh</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ananths Aphipong</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>11/28/1998</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Aidin</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ananthaphipon</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Worraphan</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Lakkham</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>04/02/2000</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Thananya</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Charnnankit</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>05/30/1999</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jidapa</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tharak</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>09/10/1999</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Isaree</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Chatchawansanoi</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>05/28/1999</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Warakorrl</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Subannakoon</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10/18/1999</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aoife Patricia</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PW5647049</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>03/27/1979</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Barry John</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PW1031468</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10/05/1979</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Alex Joseph</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PK3070672</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>07/25/2015</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Finn Niall</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PP5868175</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>09/21/2017</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jacob Tex</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PR196O031</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>09/21/2017</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Shenying</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Xiang</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>EW3952983</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>08/17/1961</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Xiaoyan</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EC5535702</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>04/13/1986</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Kalinin</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>758372349</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>04/04/2003</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Marina</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kalinina</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>775799575</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>02/06/2006</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Suleemart</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Samattanark</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>07/19/1978</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Tanai</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Phuwapraser T</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>02/26/1977</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Wallapa</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kulvanich</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>11/08/1994</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Paramin</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Kulvanich</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>04/10/1997</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Magdalena Anna</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sabik</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PE6355910</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>06/09/1984</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Wiesława</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Kvašnovska</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EU5554038</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>09/03/1955</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Marta Barbara</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nitka</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>EW6312138</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>07/04/1985</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Julian Kazimierz</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Niezgoda</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FK4782435</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>11/27/2017</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Pola Anna</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Niezgoda</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>FK7782425</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>05/13/2014</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Thanyaluk</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Buathong</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>08/22/1998</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Songyos</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Thongon</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>01/05/1998</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Arnon</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Jailak</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>09/17/1993</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Chaiyapong</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Lueanloy</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>06/15/1996</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Rajbhandari</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>10/07/1988</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Dubrovin</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>41336777</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>09/27/1983</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Nurit</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sadot Durbrovin</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>37981632</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>12/28/1981</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Itay</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Dubrovin</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>40109180</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>09/18/2016</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Oo.xlsx
+++ b/Oo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4965" yWindow="8100" windowWidth="23010" windowHeight="17820" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="675" yWindow="1770" windowWidth="16620" windowHeight="11610" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -517,34 +517,29 @@
           <t>FN</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>LN</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>NT</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>BD</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ARR</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -559,34 +554,29 @@
           <t>Lilah</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Zim</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>34947428</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>34947428</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>09/04/1978</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,34 +591,29 @@
           <t>May</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Zim</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>35134168</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35134168</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10/11/2002</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -643,34 +628,29 @@
           <t>Itay</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bachar</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>40811474</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>40811474</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>06/21/2016</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -685,34 +665,29 @@
           <t>Emma</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Zim</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>42509977</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>42509977</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>10/21/2016</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -727,24 +702,19 @@
           <t>Hen Michael</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Oron</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Israel</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -759,34 +729,29 @@
           <t>Nina</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Dabbah</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>42666121</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>42666121</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>07/25/1966</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,34 +766,29 @@
           <t>Gefen</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Oron</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>35613979</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>35613979</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>03/15/2015</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -843,34 +803,29 @@
           <t>Tevel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Oron</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>35619612</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>35619612</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>11/13/2012</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -885,29 +840,24 @@
           <t>Rusainee</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Nantha Aphipong</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>08/18/2000</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -922,29 +872,24 @@
           <t>Urai</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Naiyana</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>11/21/1961</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,34 +904,29 @@
           <t>Aleksandr</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Kalinin</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>758372349</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>758372349</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>04/04/2003</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1001,34 +941,29 @@
           <t>Tatiana</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Kalinina</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>773245745</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>773245745</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>12/09/1977</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1043,34 +978,29 @@
           <t>Sergei</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Kalinin</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>773126318</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>773126318</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>08/02/1966</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1085,29 +1015,24 @@
           <t>Thanyaluk</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Buathong</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>08/22/1998</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1122,29 +1047,24 @@
           <t>Pimporn</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Hemrat</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>03/17/1960</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1159,24 +1079,19 @@
           <t>Pattraporn</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Tongrit</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>11/24/1976</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1191,34 +1106,29 @@
           <t>Dubrovin</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Daniel</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>41336777</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>41336777</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>09/27/1983</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1233,34 +1143,29 @@
           <t>Guy</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Dubrovin</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>40090126</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>40090126</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>04/24/2012</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1275,34 +1180,29 @@
           <t>Roni</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Dubrovin</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>40109442</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>40109442</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>04/05/2011</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1317,34 +1217,29 @@
           <t>Carmen Maree</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Greenhill</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PB4215303</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PB4215303</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>05/15/1977</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1359,34 +1254,29 @@
           <t>Matthew Byron</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Greenhill</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PB3047057</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PB3047057</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>09/03/1975</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1401,34 +1291,29 @@
           <t>Alannah Maree</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Greenhill</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PB4227658</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>PB4227658</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>07/29/2010</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1443,34 +1328,29 @@
           <t>Bridget Carmen</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Greenhill</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PB4705835</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PB4705835</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>07/01/2014</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1485,34 +1365,29 @@
           <t>Daniel Warwick</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Greenhill</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PB4227679</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>PB4227679</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>09/10/2008</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1527,34 +1402,29 @@
           <t>Kelly Ann</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Parker</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RA6294943</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RA6294943</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>05/05/1990</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1569,34 +1439,29 @@
           <t>Zoey Ann</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Parker</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RA1102741</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RA1102741</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>12/14/2020</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1611,34 +1476,29 @@
           <t>Zane Lawrence</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Parker</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RA5552607</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RA5552607</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>05/31/2019</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1653,34 +1513,29 @@
           <t>Mitchell Daine</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Parker</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RA6181807</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RA6181807</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>11/14/1988</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1695,34 +1550,29 @@
           <t>Grant James</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Wolfel</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PA6284807</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>PA6284807</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>11/02/1983</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1737,34 +1587,29 @@
           <t>Edward James</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Wolfel</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PB5188808</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>PB5188808</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>04/20/2017</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1779,34 +1624,29 @@
           <t>Sarah Elizabeth</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Wolfel</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RA6949831</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RA6949831</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>09/05/1983</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1821,34 +1661,29 @@
           <t>Jack Grant</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Wolfel</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RA6059493</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RA6059493</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>08/24/2023</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1863,34 +1698,29 @@
           <t>Sophie Grace</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Wolfel</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PB6339145</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PB6339145</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>05/08/2019</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1905,34 +1735,29 @@
           <t>Sarah Ann</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Hartley</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PB6176114</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PB6176114</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>02/08/1990</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1947,34 +1772,29 @@
           <t>Adam Lee</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Clarke</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PB4687758</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PB4687758</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>01/24/1987</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1989,34 +1809,29 @@
           <t>Riley Hartley</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Clarke</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RA5905033</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RA5905033</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>07/15/2023</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2031,34 +1846,29 @@
           <t>Paige Hartley</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Clarke</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PB6252899</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>PB6252899</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>10/15/2019</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2073,29 +1883,24 @@
           <t>Gerard</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Francisduignan</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>10/16/1984</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2110,29 +1915,24 @@
           <t>Sinit</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Duignan</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>05/03/1985</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2147,34 +1947,29 @@
           <t>Nitsan</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Vaknin</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>42207675</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>42207675</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>03/18/1984</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2189,34 +1984,29 @@
           <t>Rani</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Vaknin</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>42980162</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>42980162</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>12/15/2025</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2231,34 +2021,29 @@
           <t>Lavie</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Vaknin</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>42200373</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>42200373</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>11/11/2019</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2273,34 +2058,29 @@
           <t>Tom Raphael</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Vaknin</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>42202548</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>42202548</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>11/03/2015</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2315,34 +2095,29 @@
           <t>Yael Viki</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Vaknin Gaizler</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>33153656</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>33153656</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>10/27/1987</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2357,34 +2132,29 @@
           <t>David James</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Wilkins</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>120297461</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>120297461</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>11/11/1978</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2399,34 +2169,29 @@
           <t>Ruby Rose</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Wilkins</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>157875017</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>157875017</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>04/16/2011</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2441,34 +2206,29 @@
           <t>Beverley Louise</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Wilkins</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>557796941</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>557796941</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>01/22/1976</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2483,34 +2243,29 @@
           <t>Florence Rose</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Wilkins</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>128764091</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>128764091</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>10/15/2017</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2525,34 +2280,29 @@
           <t>David James</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Wilkins</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>120297461</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>120297461</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>11/11/1978</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2567,34 +2317,29 @@
           <t>Margaret Rose</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Wilkins</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>159875255</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>159875255</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>11/18/2015</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2609,34 +2354,29 @@
           <t>Constance Rose</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Wilkins</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>157409532</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>157409532</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>11/18/2015</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2651,34 +2391,29 @@
           <t>Andrew George</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Deane</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RA5109542</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RA5109542</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>12/22/1971</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2693,34 +2428,29 @@
           <t>Zoe Louisa</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Deane</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PB5197823</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>PB5197823</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>12/09/2014</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2735,34 +2465,29 @@
           <t>Aletia Maree</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Deane</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RA9752915</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RA9752915</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>04/29/1978</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2777,34 +2502,29 @@
           <t>Lily Elise</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Deane</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PB4748359</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>PB4748359</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>11/10/2010</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2819,34 +2539,29 @@
           <t>Lirit</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Bachar</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>37837824</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>37837824</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>12/18/1981</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2861,34 +2576,29 @@
           <t>Lia</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Bachar</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>40812440</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>40812440</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>08/21/2009</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2903,34 +2613,29 @@
           <t>Yakov</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Bachar</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>43051860</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>43051860</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>02/21/1981</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2945,34 +2650,29 @@
           <t>Roni</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Bachar</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40818730</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>40818730</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>06/01/2013</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2987,34 +2687,29 @@
           <t>Liran Yehuda</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Bachar</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40819657</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>40819657</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>04/21/2011</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3029,34 +2724,29 @@
           <t>Maayan</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Oron</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>24688189</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>24688189</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>10/23/1988</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3071,34 +2761,29 @@
           <t>Hen Michael</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Oron</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40082484</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>40082484</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>12/10/1984</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3113,34 +2798,29 @@
           <t>Shoham</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Oron</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40089310</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>40089310</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>02/02/2018</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3155,29 +2835,24 @@
           <t>Irene</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Anantha Aphipon</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>08/30/1998</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3192,29 +2867,24 @@
           <t>Aimulloh</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Ananths Aphipong</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>11/28/1998</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3229,29 +2899,24 @@
           <t>Aidin</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Ananthaphipon</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>01/16/2026</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3266,29 +2931,24 @@
           <t>Worraphan</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Lakkham</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>04/02/2000</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3303,29 +2963,24 @@
           <t>Thananya</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Charnnankit</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>05/30/1999</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3340,29 +2995,24 @@
           <t>Jidapa</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Tharak</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>09/10/1999</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3377,29 +3027,24 @@
           <t>Isaree</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Chatchawansanoi</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>05/28/1999</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3414,29 +3059,24 @@
           <t>Warakorrl</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Subannakoon</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>10/18/1999</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3451,34 +3091,29 @@
           <t>Aoife Patricia</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Cahill</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PW5647049</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>PW5647049</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>03/27/1979</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3493,34 +3128,29 @@
           <t>Barry John</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Cahill</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PW1031468</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>PW1031468</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>10/05/1979</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3535,34 +3165,29 @@
           <t>Alex Joseph</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Cahill</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PK3070672</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>PK3070672</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>07/25/2015</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3577,34 +3202,29 @@
           <t>Finn Niall</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Cahill</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PP5868175</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>PP5868175</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>09/21/2017</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3619,34 +3239,29 @@
           <t>Jacob Tex</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Cahill</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PR196O031</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>PR196O031</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>09/21/2017</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3661,34 +3276,29 @@
           <t>Shenying</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Xiang</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>EW3952983</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>EW3952983</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>08/17/1961</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3703,34 +3313,29 @@
           <t>Xiaoyan</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Wang</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EC5535702</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>EC5535702</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>04/13/1986</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3745,34 +3350,29 @@
           <t>Aleksandr</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Kalinin</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>758372349</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>758372349</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>04/04/2003</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3787,34 +3387,29 @@
           <t>Marina</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Kalinina</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>775799575</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>775799575</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>02/06/2006</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3829,29 +3424,24 @@
           <t>Suleemart</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Samattanark</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>07/19/1978</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3866,29 +3456,24 @@
           <t>Tanai</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Phuwapraser T</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>02/26/1977</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3903,29 +3488,24 @@
           <t>Wallapa</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Kulvanich</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>11/08/1994</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3940,29 +3520,24 @@
           <t>Paramin</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Kulvanich</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>04/10/1997</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3977,34 +3552,29 @@
           <t>Magdalena Anna</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Sabik</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PE6355910</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>PE6355910</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>06/09/1984</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4019,34 +3589,29 @@
           <t>Wiesława</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Kvašnovska</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EU5554038</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>EU5554038</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>09/03/1955</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4061,34 +3626,29 @@
           <t>Marta Barbara</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Nitka</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>EW6312138</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>EW6312138</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>07/04/1985</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4103,34 +3663,29 @@
           <t>Julian Kazimierz</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Niezgoda</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FK4782435</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>FK4782435</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>11/27/2017</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4145,34 +3700,29 @@
           <t>Pola Anna</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Niezgoda</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>FK7782425</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>FK7782425</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>05/13/2014</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4187,29 +3737,24 @@
           <t>Thanyaluk</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Buathong</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>08/22/1998</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4224,29 +3769,24 @@
           <t>Songyos</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Thongon</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>01/05/1998</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4261,29 +3801,24 @@
           <t>Arnon</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Jailak</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>09/17/1993</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4298,29 +3833,24 @@
           <t>Chaiyapong</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Lueanloy</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>06/15/1996</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4335,24 +3865,19 @@
           <t>Rajbhandari</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Roman</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>10/07/1988</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4367,34 +3892,29 @@
           <t>Dubrovin</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Daniel</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>41336777</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>41336777</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>09/27/1983</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4409,34 +3929,29 @@
           <t>Nurit</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Sadot Durbrovin</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>37981632</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>37981632</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>12/28/1981</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4451,34 +3966,29 @@
           <t>Itay</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Dubrovin</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>40109180</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>40109180</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>09/18/2016</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">

--- a/Oo.xlsx
+++ b/Oo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="675" yWindow="1770" windowWidth="16620" windowHeight="11610" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4035" yWindow="3630" windowWidth="20010" windowHeight="13815" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -413,8 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" bestFit="1" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -495,6 +498,37 @@
         <is>
           <t>40090126</t>
         </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tongrit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pattraporn</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>35012000</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Oron</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hen Michael</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102003004</v>
       </c>
     </row>
   </sheetData>
@@ -508,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,17 +605,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>09/04/1978</t>
+          <t>04/09/1978</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
@@ -608,17 +642,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10/11/2002</t>
+          <t>11/10/2002</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
@@ -645,17 +679,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06/21/2016</t>
+          <t>21/06/2016</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
@@ -682,17 +716,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/21/2016</t>
+          <t>21/10/2016</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
@@ -712,14 +746,19 @@
           <t>M</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>102003004</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -746,17 +785,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>07/25/1966</t>
+          <t>25/07/1966</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -783,17 +822,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>03/15/2015</t>
+          <t>15/03/2015</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -820,61 +859,66 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11/13/2012</t>
+          <t>13/11/2012</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rusainee</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nantha Aphipong</t>
+          <t>Kalinin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>758372349</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>08/18/2000</t>
+          <t>04/04/2003</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Urai</t>
+          <t>Tatiana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Naiyana</t>
+          <t>Kalinina</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -882,26 +926,31 @@
           <t>F</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>773245745</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11/21/1961</t>
+          <t>09/12/1977</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Sergei</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -916,71 +965,66 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>758372349</t>
+          <t>773126318</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>04/04/2003</t>
+          <t>02/08/1966</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tatiana</t>
+          <t>Pattraporn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kalinina</t>
+          <t>Tongrit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>773245745</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Russia</t>
+          <t>35012000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12/09/1977</t>
+          <t>24/11/1976</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sergei</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kalinin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -990,66 +1034,71 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>773126318</t>
+          <t>41336777</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>08/02/1966</t>
+          <t>27/09/1983</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thanyaluk</t>
+          <t>Guy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Buathong</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>40090126</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>08/22/1998</t>
+          <t>24/04/2012</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pimporn</t>
+          <t>Roni</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hemrat</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1057,58 +1106,73 @@
           <t>F</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>40109442</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>03/17/1960</t>
+          <t>05/04/2011</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pattraporn</t>
+          <t>Carmen Maree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tongrit</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PB4215303</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11/24/1976</t>
+          <t>15/05/1977</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dubrovin</t>
+          <t>Matthew Byron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1118,71 +1182,71 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41336777</t>
+          <t>PB3047057</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>09/27/1983</t>
+          <t>03/09/1975</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Guy</t>
+          <t>Alannah Maree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dubrovin</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40090126</t>
+          <t>PB4227658</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>04/24/2012</t>
+          <t>29/07/2010</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Roni</t>
+          <t>Bridget Carmen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dubrovin</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1192,29 +1256,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>40109442</t>
+          <t>PB4705835</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>04/05/2011</t>
+          <t>01/07/2014</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Carmen Maree</t>
+          <t>Daniel Warwick</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1224,76 +1288,76 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PB4215303</t>
+          <t>PB4227679</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/15/1977</t>
+          <t>10/09/2008</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Matthew Byron</t>
+          <t>Kelly Ann</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PB3047057</t>
+          <t>RA6294943</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>09/03/1975</t>
+          <t>05/05/1990</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alannah Maree</t>
+          <t>Zoey Ann</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1303,71 +1367,71 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PB4227658</t>
+          <t>RA1102741</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>07/29/2010</t>
+          <t>14/12/2020</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bridget Carmen</t>
+          <t>Zane Lawrence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PB4705835</t>
+          <t>RA5552607</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>07/01/2014</t>
+          <t>31/05/2019</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniel Warwick</t>
+          <t>Mitchell Daine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1377,145 +1441,145 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PB4227679</t>
+          <t>RA6181807</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>09/10/2008</t>
+          <t>14/11/1988</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kelly Ann</t>
+          <t>Grant James</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RA6294943</t>
+          <t>PA6284807</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/05/1990</t>
+          <t>02/11/1983</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zoey Ann</t>
+          <t>Edward James</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RA1102741</t>
+          <t>PB5188808</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12/14/2020</t>
+          <t>20/04/2017</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zane Lawrence</t>
+          <t>Sarah Elizabeth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RA5552607</t>
+          <t>RA6949831</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/31/2019</t>
+          <t>05/09/1983</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mitchell Daine</t>
+          <t>Jack Grant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1525,29 +1589,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RA6181807</t>
+          <t>RA6059493</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11/14/1988</t>
+          <t>24/08/2023</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grant James</t>
+          <t>Sophie Grace</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1557,150 +1621,150 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PA6284807</t>
+          <t>PB6339145</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11/02/1983</t>
+          <t>08/05/2019</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Edward James</t>
+          <t>Sarah Ann</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PB5188808</t>
+          <t>PB6176114</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>04/20/2017</t>
+          <t>08/02/1990</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sarah Elizabeth</t>
+          <t>Adam Lee</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Clarke</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RA6949831</t>
+          <t>PB4687758</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>09/05/1983</t>
+          <t>24/01/1987</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jack Grant</t>
+          <t>Riley Hartley</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Clarke</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RA6059493</t>
+          <t>RA5905033</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>08/24/2023</t>
+          <t>15/07/2023</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sophie Grace</t>
+          <t>Paige Hartley</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Clarke</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1710,71 +1774,71 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PB6339145</t>
+          <t>PB6252899</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>05/08/2019</t>
+          <t>15/10/2019</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sarah Ann</t>
+          <t>Nitsan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PB6176114</t>
+          <t>42207675</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>02/08/1990</t>
+          <t>18/03/1984</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>07/16/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Adam Lee</t>
+          <t>Rani</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Clarke</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1784,283 +1848,293 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PB4687758</t>
+          <t>42980162</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01/24/1987</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>07/16/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Riley Hartley</t>
+          <t>Lavie</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Clarke</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RA5905033</t>
+          <t>42200373</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>07/15/2023</t>
+          <t>11/11/2019</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>07/16/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Paige Hartley</t>
+          <t>Tom Raphael</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Clarke</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PB6252899</t>
+          <t>42202548</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10/15/2019</t>
+          <t>03/11/2015</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>07/16/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gerard</t>
+          <t>Yael Viki</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Francisduignan</t>
+          <t>Vaknin Gaizler</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>33153656</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10/16/1984</t>
+          <t>27/10/1987</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sinit</t>
+          <t>David James</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Duignan</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>120297461</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/03/1985</t>
+          <t>11/11/1978</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nitsan</t>
+          <t>Ruby Rose</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42207675</t>
+          <t>157875017</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>03/18/1984</t>
+          <t>16/04/2011</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rani</t>
+          <t>Beverley Louise</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>42980162</t>
+          <t>557796941</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>22/01/1976</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lavie</t>
+          <t>Florence Rose</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>42200373</t>
+          <t>128764091</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11/11/2019</t>
+          <t>15/10/2017</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tom Raphael</t>
+          <t>David James</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2070,34 +2144,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>42202548</t>
+          <t>120297461</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11/03/2015</t>
+          <t>11/11/1978</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Yael Viki</t>
+          <t>Margaret Rose</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vaknin Gaizler</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2107,29 +2181,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33153656</t>
+          <t>159875255</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>10/27/1987</t>
+          <t>18/11/2015</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>David James</t>
+          <t>Constance Rose</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2139,76 +2213,76 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>120297461</t>
+          <t>157409532</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11/11/1978</t>
+          <t>18/11/2015</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ruby Rose</t>
+          <t>Andrew George</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>157875017</t>
+          <t>RA5109542</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>04/16/2011</t>
+          <t>22/12/1971</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Beverley Louise</t>
+          <t>Zoe Louisa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2218,34 +2292,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>557796941</t>
+          <t>PB5197823</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01/22/1976</t>
+          <t>09/12/2014</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Florence Rose</t>
+          <t>Aletia Maree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2255,71 +2329,71 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>128764091</t>
+          <t>RA9752915</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>10/15/2017</t>
+          <t>29/04/1978</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>David James</t>
+          <t>Lily Elise</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>120297461</t>
+          <t>PB4748359</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11/11/1978</t>
+          <t>10/11/2010</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Margaret Rose</t>
+          <t>Lirit</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2329,34 +2403,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>159875255</t>
+          <t>37837824</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11/18/2015</t>
+          <t>18/12/1981</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Constance Rose</t>
+          <t>Lia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2366,34 +2440,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>157409532</t>
+          <t>40812440</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>11/18/2015</t>
+          <t>21/08/2009</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Andrew George</t>
+          <t>Yakov</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2403,34 +2477,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RA5109542</t>
+          <t>43051860</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12/22/1971</t>
+          <t>21/02/1981</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Zoe Louisa</t>
+          <t>Roni</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2440,71 +2514,71 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PB5197823</t>
+          <t>40818730</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>12/09/2014</t>
+          <t>01/06/2013</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Aletia Maree</t>
+          <t>Liran Yehuda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RA9752915</t>
+          <t>40819657</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>04/29/1978</t>
+          <t>21/04/2011</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lily Elise</t>
+          <t>Maayan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Oron</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2514,182 +2588,182 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PB4748359</t>
+          <t>24688189</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11/10/2010</t>
+          <t>23/10/1988</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lirit</t>
+          <t>Hen Michael</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Oron</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>37837824</t>
+          <t>102003004</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>12/18/1981</t>
+          <t>10/12/1984</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lia</t>
+          <t>Shoham</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Oron</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>40812440</t>
+          <t>40089310</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>08/21/2009</t>
+          <t>02/02/2018</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Yakov</t>
+          <t>Aoife Patricia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Cahill</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>43051860</t>
+          <t>PW5647049</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>02/21/1981</t>
+          <t>27/03/1979</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Roni</t>
+          <t>Barry John</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Cahill</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>40818730</t>
+          <t>PW1031468</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>06/01/2013</t>
+          <t>05/10/1979</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Liran Yehuda</t>
+          <t>Alex Joseph</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Cahill</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2699,71 +2773,71 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>40819657</t>
+          <t>PK3070672</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>04/21/2011</t>
+          <t>25/07/2015</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Maayan</t>
+          <t>Finn Niall</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oron</t>
+          <t>Cahill</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>24688189</t>
+          <t>PP5868175</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>10/23/1988</t>
+          <t>21/09/2017</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hen Michael</t>
+          <t>Jacob Tex</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oron</t>
+          <t>Cahill</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2773,71 +2847,71 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40082484</t>
+          <t>PR196O031</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>12/10/1984</t>
+          <t>21/09/2017</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Shoham</t>
+          <t>Shenying</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oron</t>
+          <t>Xiang</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>40089310</t>
+          <t>EW3952983</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>02/02/2018</t>
+          <t>17/08/1961</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Irene</t>
+          <t>Xiaoyan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Anantha Aphipon</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2845,31 +2919,36 @@
           <t>F</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>EC5535702</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>08/30/1998</t>
+          <t>13/04/1986</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aimulloh</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ananths Aphipong</t>
+          <t>Kalinin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2877,63 +2956,73 @@
           <t>M</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>758372349</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>11/28/1998</t>
+          <t>04/04/2003</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aidin</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ananthaphipon</t>
+          <t>Kalinina</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>775799575</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01/16/2026</t>
+          <t>06/02/2006</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Worraphan</t>
+          <t>Magdalena Anna</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lakkham</t>
+          <t>Sabik</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2941,31 +3030,36 @@
           <t>F</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PE6355910</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>04/02/2000</t>
+          <t>09/06/1984</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Thananya</t>
+          <t>Wiesława</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charnnankit</t>
+          <t>Kvašnovska</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2973,31 +3067,36 @@
           <t>F</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>EU5554038</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>05/30/1999</t>
+          <t>03/09/1955</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jidapa</t>
+          <t>Marta Barbara</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tharak</t>
+          <t>Nitka</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3005,993 +3104,207 @@
           <t>F</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>EW6312138</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>09/10/1999</t>
+          <t>04/07/1985</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Isaree</t>
+          <t>Julian Kazimierz</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chatchawansanoi</t>
+          <t>Niezgoda</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>FK4782435</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>05/28/1999</t>
+          <t>27/11/2017</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Warakorrl</t>
+          <t>Pola Anna</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Subannakoon</t>
+          <t>Niezgoda</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>FK7782425</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>10/18/1999</t>
+          <t>13/05/2014</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aoife Patricia</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PW5647049</t>
+          <t>41336777</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>03/27/1979</t>
+          <t>27/09/1983</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Barry John</t>
+          <t>Nurit</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Sadot Durbrovin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PW1031468</t>
+          <t>37981632</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>10/05/1979</t>
+          <t>28/12/1981</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alex Joseph</t>
+          <t>Itay</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PK3070672</t>
+          <t>40109180</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>07/25/2015</t>
+          <t>18/09/2016</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Finn Niall</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Cahill</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>PP5868175</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>09/21/2017</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Jacob Tex</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Cahill</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>PR196O031</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>09/21/2017</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Shenying</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Xiang</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>EW3952983</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>08/17/1961</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Xiaoyan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>EC5535702</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>04/13/1986</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Aleksandr</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Kalinin</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>758372349</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>04/04/2003</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>07/14/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Marina</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Kalinina</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>775799575</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>02/06/2006</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>07/14/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Suleemart</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Samattanark</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>07/19/1978</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Tanai</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Phuwapraser T</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>02/26/1977</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Wallapa</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Kulvanich</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>11/08/1994</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Paramin</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Kulvanich</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>04/10/1997</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Magdalena Anna</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Sabik</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>PE6355910</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>06/09/1984</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>07/15/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Wiesława</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Kvašnovska</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>EU5554038</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>09/03/1955</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>07/15/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Marta Barbara</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Nitka</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>EW6312138</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>07/04/1985</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>07/15/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Julian Kazimierz</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Niezgoda</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>FK4782435</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>11/27/2017</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>07/15/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Pola Anna</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Niezgoda</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>FK7782425</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>05/13/2014</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>07/15/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Thanyaluk</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Buathong</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>08/22/1998</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Songyos</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Thongon</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>01/05/1998</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Arnon</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Jailak</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>09/17/1993</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Chaiyapong</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Lueanloy</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>06/15/1996</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Rajbhandari</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Roman</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>10/07/1988</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Dubrovin</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>41336777</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>09/27/1983</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Nurit</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Sadot Durbrovin</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>37981632</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>12/28/1981</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Itay</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Dubrovin</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>40109180</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>09/18/2016</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>

--- a/Oo.xlsx
+++ b/Oo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4035" yWindow="3630" windowWidth="20010" windowHeight="13815" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="495" yWindow="990" windowWidth="14370" windowHeight="11820" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -529,6 +529,21 @@
       </c>
       <c r="E6" t="n">
         <v>102003004</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Zim</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lilah</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100002</v>
       </c>
     </row>
   </sheetData>
@@ -542,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,11 +618,6 @@
           <t>34947428</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>04/09/1978</t>
@@ -640,11 +650,6 @@
           <t>35134168</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>11/10/2002</t>
@@ -677,11 +682,6 @@
           <t>40811474</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>21/06/2016</t>
@@ -714,11 +714,6 @@
           <t>42509977</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>21/10/2016</t>
@@ -751,11 +746,6 @@
           <t>102003004</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>08/07/2026</t>
@@ -783,11 +773,6 @@
           <t>42666121</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>25/07/1966</t>
@@ -820,11 +805,6 @@
           <t>35613979</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>15/03/2015</t>
@@ -857,11 +837,6 @@
           <t>35619612</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>13/11/2012</t>
@@ -876,49 +851,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Rusainee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kalinin</t>
+          <t>Nantha Aphipong</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>758372349</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>RUS</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>04/04/2003</t>
+          <t>18/08/2000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tatiana</t>
+          <t>Urai</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kalinina</t>
+          <t>Naiyana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -926,31 +891,21 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>773245745</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>09/12/1977</t>
+          <t>21/11/1961</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sergei</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -965,17 +920,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>773126318</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>RUS</t>
+          <t>758372349</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>02/08/1966</t>
+          <t>04/04/2003</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,44 +937,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pattraporn</t>
+          <t>Tatiana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tongrit</t>
+          <t>Kalinina</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35012000</t>
+          <t>773245745</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>24/11/1976</t>
+          <t>09/12/1977</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dubrovin</t>
+          <t>Sergei</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Kalinin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1034,71 +984,56 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41336777</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>773126318</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27/09/1983</t>
+          <t>02/08/1966</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Guy</t>
+          <t>Thanyaluk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dubrovin</t>
+          <t>Buathong</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>40090126</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24/04/2012</t>
+          <t>22/08/1998</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Roni</t>
+          <t>Pimporn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dubrovin</t>
+          <t>Hemrat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,73 +1041,58 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>40109442</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/04/2011</t>
+          <t>17/03/1960</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Carmen Maree</t>
+          <t>Pattraporn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Tongrit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PB4215303</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>35012000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15/05/1977</t>
+          <t>24/11/1976</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Matthew Byron</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1182,71 +1102,61 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PB3047057</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>41336777</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>03/09/1975</t>
+          <t>27/09/1983</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alannah Maree</t>
+          <t>Guy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PB4227658</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>40090126</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29/07/2010</t>
+          <t>24/04/2012</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bridget Carmen</t>
+          <t>Roni</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenhill</t>
+          <t>Dubrovin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1256,29 +1166,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PB4705835</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>40109442</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01/07/2014</t>
+          <t>05/04/2011</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daniel Warwick</t>
+          <t>Carmen Maree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1288,22 +1193,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PB4227679</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PB4215303</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10/09/2008</t>
+          <t>15/05/1977</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1315,49 +1215,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kelly Ann</t>
+          <t>Matthew Byron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RA6294943</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PB3047057</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/05/1990</t>
+          <t>03/09/1975</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zoey Ann</t>
+          <t>Alannah Maree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1367,71 +1262,61 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RA1102741</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PB4227658</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14/12/2020</t>
+          <t>29/07/2010</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zane Lawrence</t>
+          <t>Bridget Carmen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RA5552607</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PB4705835</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>31/05/2019</t>
+          <t>01/07/2014</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mitchell Daine</t>
+          <t>Daniel Warwick</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Greenhill</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1441,54 +1326,44 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RA6181807</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PB4227679</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14/11/1988</t>
+          <t>10/09/2008</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Grant James</t>
+          <t>Kelly Ann</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PA6284807</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>RA6294943</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>02/11/1983</t>
+          <t>05/05/1990</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1500,32 +1375,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Edward James</t>
+          <t>Zoey Ann</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PB5188808</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>RA1102741</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20/04/2017</t>
+          <t>14/12/2020</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1537,32 +1407,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sarah Elizabeth</t>
+          <t>Zane Lawrence</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RA6949831</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>RA5552607</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/09/1983</t>
+          <t>31/05/2019</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1574,12 +1439,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jack Grant</t>
+          <t>Mitchell Daine</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wolfel</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1589,17 +1454,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RA6059493</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>RA6181807</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>24/08/2023</t>
+          <t>14/11/1988</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1611,7 +1471,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sophie Grace</t>
+          <t>Grant James</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1621,22 +1481,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PB6339145</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PA6284807</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>08/05/2019</t>
+          <t>02/11/1983</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1648,123 +1503,108 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sarah Ann</t>
+          <t>Edward James</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PB6176114</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PB5188808</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>08/02/1990</t>
+          <t>20/04/2017</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Adam Lee</t>
+          <t>Sarah Elizabeth</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Clarke</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PB4687758</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>RA6949831</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>24/01/1987</t>
+          <t>05/09/1983</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Riley Hartley</t>
+          <t>Jack Grant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clarke</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RA5905033</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>RA6059493</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>15/07/2023</t>
+          <t>24/08/2023</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paige Hartley</t>
+          <t>Sophie Grace</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Clarke</t>
+          <t>Wolfel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1774,71 +1614,61 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PB6252899</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>PB6339145</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15/10/2019</t>
+          <t>08/05/2019</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nitsan</t>
+          <t>Sarah Ann</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>42207675</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>PB6176114</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18/03/1984</t>
+          <t>08/02/1990</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rani</t>
+          <t>Adam Lee</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Clarke</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1848,293 +1678,243 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42980162</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>PB4687758</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>24/01/1987</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lavie</t>
+          <t>Riley Hartley</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Clarke</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42200373</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>RA5905033</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11/11/2019</t>
+          <t>15/07/2023</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tom Raphael</t>
+          <t>Paige Hartley</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vaknin</t>
+          <t>Clarke</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>42202548</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>PB6252899</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>03/11/2015</t>
+          <t>15/10/2019</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Yael Viki</t>
+          <t>Gerard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vaknin Gaizler</t>
+          <t>Francisduignan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>33153656</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>27/10/1987</t>
+          <t>16/10/1984</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>David James</t>
+          <t>Sinit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Duignan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>120297461</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>GBR</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11/11/1978</t>
+          <t>03/05/1985</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ruby Rose</t>
+          <t>Nitsan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>157875017</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>GBR</t>
+          <t>42207675</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>16/04/2011</t>
+          <t>18/03/1984</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Beverley Louise</t>
+          <t>Rani</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>557796941</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>GBR</t>
+          <t>42980162</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>22/01/1976</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Florence Rose</t>
+          <t>Lavie</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>128764091</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>GBR</t>
+          <t>42200373</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>15/10/2017</t>
+          <t>11/11/2019</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>David James</t>
+          <t>Tom Raphael</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Vaknin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2144,34 +1924,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>120297461</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>GBR</t>
+          <t>42202548</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11/11/1978</t>
+          <t>03/11/2015</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Margaret Rose</t>
+          <t>Yael Viki</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Vaknin Gaizler</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2181,29 +1956,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>159875255</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>GBR</t>
+          <t>33153656</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/11/2015</t>
+          <t>27/10/1987</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Constance Rose</t>
+          <t>David James</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2213,22 +1983,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>157409532</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>GBR</t>
+          <t>120297461</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/11/2015</t>
+          <t>11/11/1978</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2240,32 +2005,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Andrew George</t>
+          <t>Ruby Rose</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RA5109542</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>157875017</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22/12/1971</t>
+          <t>16/04/2011</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2277,12 +2037,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zoe Louisa</t>
+          <t>Beverley Louise</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2292,17 +2052,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PB5197823</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>557796941</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>09/12/2014</t>
+          <t>22/01/1976</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2314,12 +2069,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aletia Maree</t>
+          <t>Florence Rose</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2329,17 +2084,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RA9752915</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>128764091</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>29/04/1978</t>
+          <t>15/10/2017</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2351,32 +2101,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lily Elise</t>
+          <t>David James</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Deane</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PB4748359</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AUS</t>
+          <t>120297461</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>10/11/2010</t>
+          <t>11/11/1978</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2388,12 +2133,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lirit</t>
+          <t>Margaret Rose</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2403,34 +2148,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>37837824</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>159875255</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18/12/1981</t>
+          <t>18/11/2015</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lia</t>
+          <t>Constance Rose</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2440,34 +2180,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>40812440</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>157409532</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21/08/2009</t>
+          <t>18/11/2015</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Yakov</t>
+          <t>Andrew George</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2477,34 +2212,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>43051860</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>RA5109542</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21/02/1981</t>
+          <t>22/12/1971</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Roni</t>
+          <t>Zoe Louisa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2514,71 +2244,61 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>40818730</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>PB5197823</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01/06/2013</t>
+          <t>09/12/2014</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Liran Yehuda</t>
+          <t>Aletia Maree</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bachar</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>40819657</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>RA9752915</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21/04/2011</t>
+          <t>29/04/1978</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Maayan</t>
+          <t>Lily Elise</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oron</t>
+          <t>Deane</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2588,128 +2308,108 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>24688189</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>PB4748359</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>23/10/1988</t>
+          <t>10/11/2010</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hen Michael</t>
+          <t>Lirit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oron</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>102003004</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>37837824</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10/12/1984</t>
+          <t>18/12/1981</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Shoham</t>
+          <t>Lia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oron</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>40089310</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>40812440</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>02/02/2018</t>
+          <t>21/08/2009</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Aoife Patricia</t>
+          <t>Yakov</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PW5647049</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>IRL</t>
+          <t>43051860</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>27/03/1979</t>
+          <t>21/02/1981</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2721,32 +2421,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Barry John</t>
+          <t>Roni</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PW1031468</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>IRL</t>
+          <t>40818730</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>05/10/1979</t>
+          <t>01/06/2013</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2758,12 +2453,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alex Joseph</t>
+          <t>Liran Yehuda</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Bachar</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2773,17 +2468,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PK3070672</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>IRL</t>
+          <t>40819657</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>25/07/2015</t>
+          <t>21/04/2011</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2795,49 +2485,44 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Finn Niall</t>
+          <t>Maayan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Oron</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PP5868175</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>IRL</t>
+          <t>24688189</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21/09/2017</t>
+          <t>23/10/1988</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jacob Tex</t>
+          <t>Hen Michael</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cahill</t>
+          <t>Oron</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2847,71 +2532,61 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PR196O031</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>IRL</t>
+          <t>40082484</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21/09/2017</t>
+          <t>10/12/1984</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Shenying</t>
+          <t>Shoham</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Xiang</t>
+          <t>Oron</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EW3952983</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>CHN</t>
+          <t>40089310</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17/08/1961</t>
+          <t>02/02/2018</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Xiaoyan</t>
+          <t>Irene</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Anantha Aphipon</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2919,36 +2594,26 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>EC5535702</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>CHN</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>13/04/1986</t>
+          <t>30/08/1998</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Aimulloh</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kalinin</t>
+          <t>Ananths Aphipong</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2956,73 +2621,53 @@
           <t>M</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>758372349</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>04/04/2003</t>
+          <t>28/11/1998</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Aidin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kalinina</t>
+          <t>Ananthaphipon</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>775799575</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>RUS</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>06/02/2006</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Magdalena Anna</t>
+          <t>Worraphan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sabik</t>
+          <t>Lakkham</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3030,36 +2675,26 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>PE6355910</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>09/06/1984</t>
+          <t>02/04/2000</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Wiesława</t>
+          <t>Thananya</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kvašnovska</t>
+          <t>Charnnankit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3067,36 +2702,26 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>EU5554038</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>03/09/1955</t>
+          <t>30/05/1999</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marta Barbara</t>
+          <t>Jidapa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nitka</t>
+          <t>Tharak</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3104,209 +2729,1522 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>EW6312138</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>04/07/1985</t>
+          <t>10/09/1999</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Julian Kazimierz</t>
+          <t>Isaree</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Niezgoda</t>
+          <t>Chatchawansanoi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>FK4782435</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>POL</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>27/11/2017</t>
+          <t>28/05/1999</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pola Anna</t>
+          <t>Warakorrl</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Niezgoda</t>
+          <t>Subannakoon</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>FK7782425</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>POL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>13/05/2014</t>
+          <t>18/10/1999</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dubrovin</t>
+          <t>Aoife Patricia</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Cahill</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>41336777</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>PW5647049</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>27/09/1983</t>
+          <t>27/03/1979</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nurit</t>
+          <t>Barry John</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sadot Durbrovin</t>
+          <t>Cahill</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>37981632</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>ISR</t>
+          <t>PW1031468</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>28/12/1981</t>
+          <t>05/10/1979</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>Alex Joseph</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PK3070672</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>25/07/2015</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Finn Niall</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PP5868175</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>21/09/2017</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jacob Tex</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Cahill</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PR196O031</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>21/09/2017</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Shenying</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Xiang</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>EW3952983</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>17/08/1961</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Xiaoyan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EC5535702</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>13/04/1986</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Kalinin</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>758372349</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>04/04/2003</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Marina</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Kalinina</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>775799575</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>06/02/2006</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Suleemart</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Samattanark</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>19/07/1978</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Tanai</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Phuwapraser T</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>26/02/1977</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Wallapa</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Kulvanich</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>08/11/1994</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Paramin</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Kulvanich</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>10/04/1997</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Magdalena Anna</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sabik</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PE6355910</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>09/06/1984</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Wiesława</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Kvašnovska</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EU5554038</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>03/09/1955</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Marta Barbara</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Nitka</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>EW6312138</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>04/07/1985</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Julian Kazimierz</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Niezgoda</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FK4782435</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>27/11/2017</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Pola Anna</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Niezgoda</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>FK7782425</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>13/05/2014</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Thanyaluk</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Buathong</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>22/08/1998</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Songyos</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Thongon</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>05/01/1998</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Arnon</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Jailak</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>17/09/1993</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Chaiyapong</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Lueanloy</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>15/06/1996</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Rajbhandari</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>07/10/1988</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Dubrovin</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>41336777</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>27/09/1983</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Nurit</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Sadot Durbrovin</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>37981632</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>28/12/1981</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>Itay</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Dubrovin</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>40109180</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>18/09/2016</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>07/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="114"/>
+    <row r="115">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="192"/>
+    <row r="193">
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Israel</t>
         </is>
       </c>
     </row>
